--- a/data/trending_integrated_20261016_11.xlsx
+++ b/data/trending_integrated_20261016_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8800</v>
+        <v>8640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+23.08%</t>
+          <t>'+20.84%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="F2" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G2" t="n">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -601,7 +601,7 @@
         <v>7430</v>
       </c>
       <c r="L2" t="n">
-        <v>8800</v>
+        <v>8920</v>
       </c>
       <c r="M2" t="n">
         <v>7300</v>
@@ -610,23 +610,23 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>138806508890</v>
+        <v>150863498885</v>
       </c>
       <c r="P2" t="n">
-        <v>8800</v>
+        <v>8920</v>
       </c>
       <c r="Q2" t="n">
         <v>2270</v>
       </c>
       <c r="R2" t="n">
-        <v>51000</v>
+        <v>47000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>인수합병 재료 기반의 텐버거 가능성과 함께 악성 매물 소화 중 신고가 경신 기대감.</t>
+          <t>인수합병 기대감, 텐버거 가능성 언급, 악성매물 소화 후 상승 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['인수합병', '텐버거', '신고가']</t>
+          <t>['인수합병', '텐버거', '악성매물']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7970</v>
+        <v>8490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.31%</t>
+          <t>'+18.74%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.26</v>
+        <v>-0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="H3" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,91 +687,91 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6570</v>
+        <v>7150</v>
       </c>
       <c r="K3" t="n">
-        <v>6850</v>
+        <v>8100</v>
       </c>
       <c r="L3" t="n">
-        <v>8540</v>
+        <v>8500</v>
       </c>
       <c r="M3" t="n">
-        <v>6630</v>
+        <v>7810</v>
       </c>
       <c r="N3" t="n">
-        <v>0.99</v>
+        <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>63241877005</v>
+        <v>35695959230</v>
       </c>
       <c r="P3" t="n">
-        <v>10300</v>
+        <v>16200</v>
       </c>
       <c r="Q3" t="n">
-        <v>952</v>
+        <v>1206</v>
       </c>
       <c r="R3" t="n">
-        <v>-9000</v>
+        <v>-7000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>군공항 이전 관련 호재와 함께 투기과열 종목 지정 및 호남 반도체 테마 상승 기대.</t>
+          <t>데이터 센터향 매출 및 중국 시장 개방 기대감 속 미국 양자컴퓨터 관련주로 분류. SPAD 200 미반영 및 9천원대 매물 소화 과제.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['군공항', '호남반도체', '투기과열']</t>
+          <t>['데이터 센터', '양자컴퓨터', '매물 소화']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8400</v>
+        <v>7920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.48%</t>
+          <t>'+8.49%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.23</v>
+        <v>-0.26</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="H4" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,60 +779,60 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7150</v>
+        <v>7300</v>
       </c>
       <c r="K4" t="n">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8500</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>7810</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="O4" t="n">
-        <v>32625280030</v>
+        <v>64708000000</v>
       </c>
       <c r="P4" t="n">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-39000</v>
+        <v>-8000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>데이터 센터향 매출 및 중국 시장 개방 기대감 속 미국 양자컴퓨터 관련주로 분류. SPAD 200 미반영 및 9천원대 매물 소화 과제.</t>
+          <t>군공항 이전 이슈, 정치권 언급, 호남 관련주 및 반도체 테마 관련 긍정적 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['데이터 센터', '양자컴퓨터', '매물 소화']</t>
+          <t>['군공항', '호남', '반도체']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9710</v>
+        <v>9590</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.84%</t>
+          <t>'+8.48%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>75659600545</v>
+        <v>77242327930</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -895,7 +895,7 @@
         <v>465</v>
       </c>
       <c r="R5" t="n">
-        <v>-110000</v>
+        <v>-160000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18610</v>
+        <v>18260</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.53%</t>
+          <t>'+4.52%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F6" t="n">
         <v>84</v>
       </c>
       <c r="G6" t="n">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>134175301465</v>
+        <v>136774457530</v>
       </c>
       <c r="P6" t="n">
         <v>28800</v>
@@ -987,23 +987,23 @@
         <v>15780</v>
       </c>
       <c r="R6" t="n">
-        <v>16000</v>
+        <v>3000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>반도체 테마 수혜주로서 글로벌 파운드리 연내 착공 및 공급망 확충 기대감.</t>
+          <t>반도체 테마 수혜 기대, 일본 및 호남 공장 관련 긍정적 전망, 글로벌 파운드리 연내 착공 뉴스.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체', '파운드리', '공급망']</t>
+          <t>['반도체', '수혜주', '파운드리']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10350</v>
+        <v>10340</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.23%</t>
+          <t>'+4.13%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>29480374240</v>
+        <v>29909555460</v>
       </c>
       <c r="P7" t="n">
         <v>19380</v>
@@ -1079,10 +1079,10 @@
         <v>3200</v>
       </c>
       <c r="R7" t="n">
-        <v>-160000</v>
+        <v>-140000</v>
       </c>
       <c r="S7" t="n">
-        <v>-2000</v>
+        <v>-3000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18830</v>
+        <v>18810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.63%</t>
+          <t>'+3.52%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F8" t="n">
         <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H8" t="n">
         <v>27.77</v>
@@ -1162,7 +1162,7 @@
         <v>27.82</v>
       </c>
       <c r="O8" t="n">
-        <v>26187000635</v>
+        <v>27094016190</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1171,10 +1171,10 @@
         <v>17210</v>
       </c>
       <c r="R8" t="n">
-        <v>84000</v>
+        <v>312000</v>
       </c>
       <c r="S8" t="n">
-        <v>70000</v>
+        <v>106000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65100</v>
+        <v>65200</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.84%</t>
+          <t>'+3.00%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F9" t="n">
         <v>69</v>
       </c>
       <c r="G9" t="n">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="H9" t="n">
         <v>22.1</v>
@@ -1254,7 +1254,7 @@
         <v>22.11</v>
       </c>
       <c r="O9" t="n">
-        <v>72359867300</v>
+        <v>74452891350</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1263,10 +1263,10 @@
         <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>64000</v>
+        <v>50000</v>
       </c>
       <c r="S9" t="n">
-        <v>5000</v>
+        <v>-24000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1314,13 +1314,13 @@
         <v>0.21</v>
       </c>
       <c r="E10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H10" t="n">
         <v>3.42</v>
@@ -1346,7 +1346,7 @@
         <v>3.21</v>
       </c>
       <c r="O10" t="n">
-        <v>31770489255</v>
+        <v>32767881045</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1355,10 +1355,10 @@
         <v>1640</v>
       </c>
       <c r="R10" t="n">
-        <v>-48000</v>
+        <v>-62000</v>
       </c>
       <c r="S10" t="n">
-        <v>-12000</v>
+        <v>-11000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1406,13 +1406,13 @@
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H11" t="n">
         <v>9.23</v>
@@ -1438,7 +1438,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>27976804675</v>
+        <v>28603505275</v>
       </c>
       <c r="P11" t="n">
         <v>24950</v>
@@ -1447,10 +1447,10 @@
         <v>17910</v>
       </c>
       <c r="R11" t="n">
-        <v>198000</v>
+        <v>435000</v>
       </c>
       <c r="S11" t="n">
-        <v>-21000</v>
+        <v>-20000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>214250</v>
+        <v>214500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.02%</t>
+          <t>'+2.14%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="G12" t="n">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="H12" t="n">
         <v>45.98</v>
@@ -1530,7 +1530,7 @@
         <v>46.16</v>
       </c>
       <c r="O12" t="n">
-        <v>1521149526000</v>
+        <v>1564943018500</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1539,14 +1539,14 @@
         <v>94500</v>
       </c>
       <c r="R12" t="n">
-        <v>-865000</v>
+        <v>-684000</v>
       </c>
       <c r="S12" t="n">
-        <v>111000</v>
+        <v>-108000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>이재명 정부에 대한 정치적 비판과 함께 외인 매도량 및 유가 상승에 대한 우려가 혼재됨.</t>
+          <t>정치적 이슈와 노조 관련 언급, 외인 매도량 분석, 유가 상승 우려 등 복합적인 부정적 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['이재명', '외인매도', '유가']</t>
+          <t>['외인매도', '유가', '노조']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1286000</v>
+        <v>1289000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.90%</t>
+          <t>'+2.14%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G13" t="n">
-        <v>1289</v>
+        <v>1246</v>
       </c>
       <c r="H13" t="n">
         <v>48.85</v>
@@ -1622,7 +1622,7 @@
         <v>49.02</v>
       </c>
       <c r="O13" t="n">
-        <v>2667753543000</v>
+        <v>2730533873500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1631,14 +1631,14 @@
         <v>420500</v>
       </c>
       <c r="R13" t="n">
-        <v>-291000</v>
+        <v>-448000</v>
       </c>
       <c r="S13" t="n">
-        <v>58000</v>
+        <v>-27000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 불만과 함께 최태원 회장의 책임론 및 솔리다임 중복 상장 계획 취소 요구.</t>
+          <t>정치적 이슈와 연계된 부정적 언급, 외인 비중 축소 및 개미 투자자 매수세에 대한 회의적인 시각.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['이재명', '최태원', '솔리다임']</t>
+          <t>['외인비중', '개미', '반대매매']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,83 +1667,83 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14890</v>
+        <v>41350</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.50%</t>
+          <t>'+1.47%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>96</v>
+        <v>200</v>
       </c>
       <c r="F14" t="n">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="G14" t="n">
-        <v>139</v>
+        <v>796</v>
       </c>
       <c r="H14" t="n">
-        <v>9.779999999999999</v>
+        <v>12.97</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14670</v>
+        <v>40750</v>
       </c>
       <c r="K14" t="n">
-        <v>14800</v>
+        <v>40600</v>
       </c>
       <c r="L14" t="n">
-        <v>15270</v>
+        <v>41450</v>
       </c>
       <c r="M14" t="n">
-        <v>14800</v>
+        <v>40050</v>
       </c>
       <c r="N14" t="n">
-        <v>9.710000000000001</v>
+        <v>12.84</v>
       </c>
       <c r="O14" t="n">
-        <v>20850627450</v>
+        <v>7812397275</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>69200</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>24150</v>
       </c>
       <c r="R14" t="n">
-        <v>-47000</v>
+        <v>15000</v>
       </c>
       <c r="S14" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>이재명 대통령의 주가 조작 묵인 의혹 제기와 금감원 사모펀드 긴급 점검에 대한 비판.</t>
+          <t>HLB의 담관암 FDA 승인 관련 기대감과 함께 진양곤 회장의 IR 활동 및 외인 매수세 확인.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가조작', '이재명', '사모펀드']</t>
+          <t>['HLB', 'FDA승인', '진양곤']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15100</v>
+        <v>14880</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.07%</t>
+          <t>'+1.43%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="F15" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="H15" t="n">
-        <v>0.11</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14940</v>
+        <v>14670</v>
       </c>
       <c r="K15" t="n">
-        <v>14940</v>
+        <v>14800</v>
       </c>
       <c r="L15" t="n">
-        <v>16290</v>
+        <v>15270</v>
       </c>
       <c r="M15" t="n">
-        <v>14330</v>
+        <v>14800</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>37028055110</v>
+        <v>21526973655</v>
       </c>
       <c r="P15" t="n">
-        <v>30800</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>9810</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>19000</v>
+        <v>-92000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>상장 사기 의혹 및 무능한 경영진 비판과 함께 코스닥 상장 시 시총 2천억 기대.</t>
+          <t>주가 조작 의혹과 정치적 개입 비판, 공매도 관련 언급 등 강한 부정적 심리.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['상장사기', '경영진', '코스닥']</t>
+          <t>['주가조작', '공매도', '정치']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>41150</v>
+        <v>14930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.98%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="F16" t="n">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="G16" t="n">
-        <v>783</v>
+        <v>121</v>
       </c>
       <c r="H16" t="n">
-        <v>12.97</v>
+        <v>0.11</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>40750</v>
+        <v>14940</v>
       </c>
       <c r="K16" t="n">
-        <v>40600</v>
+        <v>14940</v>
       </c>
       <c r="L16" t="n">
-        <v>41450</v>
+        <v>16290</v>
       </c>
       <c r="M16" t="n">
-        <v>40050</v>
+        <v>14330</v>
       </c>
       <c r="N16" t="n">
-        <v>12.84</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>7391743875</v>
+        <v>37949468880</v>
       </c>
       <c r="P16" t="n">
-        <v>69200</v>
+        <v>30800</v>
       </c>
       <c r="Q16" t="n">
-        <v>24150</v>
+        <v>9810</v>
       </c>
       <c r="R16" t="n">
-        <v>-4000</v>
+        <v>7000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>HLB의 담관암 FDA 승인 관련 기대감과 함께 진양곤 회장의 IR 활동 및 외인 매수세 확인.</t>
+          <t>상장 사기 의혹, 경영진 비판, 거래량 및 시가총액 관련 부정적 평가.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['HLB', 'FDA승인', '진양곤']</t>
+          <t>['상장사기', '경영진', '시가총액']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20000</v>
+        <v>19990</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-3.66%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2.5</v>
       </c>
       <c r="E17" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G17" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H17" t="n">
         <v>4.28</v>
@@ -1990,7 +1990,7 @@
         <v>1.78</v>
       </c>
       <c r="O17" t="n">
-        <v>33156756660</v>
+        <v>33724728110</v>
       </c>
       <c r="P17" t="n">
         <v>22450</v>
@@ -1999,7 +1999,7 @@
         <v>6320</v>
       </c>
       <c r="R17" t="n">
-        <v>20000</v>
+        <v>28000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27650</v>
+        <v>27200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.11%</t>
+          <t>'-7.64%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2056,10 +2056,10 @@
         <v>54</v>
       </c>
       <c r="G18" t="n">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="H18" t="n">
-        <v>53.47</v>
+        <v>53.42</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2076,13 +2076,13 @@
         <v>29600</v>
       </c>
       <c r="M18" t="n">
-        <v>27450</v>
+        <v>27150</v>
       </c>
       <c r="N18" t="n">
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>76886450875</v>
+        <v>85254968975</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>
@@ -2091,10 +2091,10 @@
         <v>21000</v>
       </c>
       <c r="R18" t="n">
-        <v>-9000</v>
+        <v>-355000</v>
       </c>
       <c r="S18" t="n">
-        <v>-57000</v>
+        <v>-111000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/data/trending_integrated_20261016_11.xlsx
+++ b/data/trending_integrated_20261016_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8640</v>
+        <v>8660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.84%</t>
+          <t>'+21.12%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G2" t="n">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -610,7 +610,7 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>150863498885</v>
+        <v>155039289960</v>
       </c>
       <c r="P2" t="n">
         <v>8920</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>인수합병 기대감, 텐버거 가능성 언급, 악성매물 소화 후 상승 전망.</t>
+          <t>인수합병 및 편입 기대감으로 인한 강한 상승세. 텐버거 가능성 등 과감한 목표가 제시. 악성매물 소화 및 신고가 경신 기대감 고조.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['인수합병', '텐버거', '악성매물']</t>
+          <t>['인수합병', '텐버거', '신고가']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8490</v>
+        <v>7800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.74%</t>
+          <t>'+18.72%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.23</v>
+        <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
-        <v>113</v>
+        <v>162</v>
       </c>
       <c r="H3" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,91 +687,91 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7150</v>
+        <v>6570</v>
       </c>
       <c r="K3" t="n">
-        <v>8100</v>
+        <v>6850</v>
       </c>
       <c r="L3" t="n">
-        <v>8500</v>
+        <v>8540</v>
       </c>
       <c r="M3" t="n">
-        <v>7810</v>
+        <v>6630</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>35695959230</v>
+        <v>65737554835</v>
       </c>
       <c r="P3" t="n">
-        <v>16200</v>
+        <v>10300</v>
       </c>
       <c r="Q3" t="n">
-        <v>1206</v>
+        <v>952</v>
       </c>
       <c r="R3" t="n">
-        <v>-7000</v>
+        <v>-8000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>데이터 센터향 매출 및 중국 시장 개방 기대감 속 미국 양자컴퓨터 관련주로 분류. SPAD 200 미반영 및 9천원대 매물 소화 과제.</t>
+          <t>군공항 이전 이슈와 호남 반도체 관련 뉴스로 인한 급등세. 신고가 경신 시 8만원 돌파 가능성 언급. 투기성 수급 유입 확인.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['데이터 센터', '양자컴퓨터', '매물 소화']</t>
+          <t>['군공항 이전', '호남 반도체', '투기']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7920</v>
+        <v>8330</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.49%</t>
+          <t>'+16.50%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.26</v>
+        <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="H4" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,60 +779,60 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7300</v>
+        <v>7150</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>8600</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>7810</v>
       </c>
       <c r="N4" t="n">
-        <v>0.99</v>
+        <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>64708000000</v>
+        <v>40943864705</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="R4" t="n">
-        <v>-8000</v>
+        <v>-7000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>군공항 이전 이슈, 정치권 언급, 호남 관련주 및 반도체 테마 관련 긍정적 전망.</t>
+          <t>데이터 센터향 매출 및 중국 시장 개방 기대감 속 미국 양자컴퓨터 관련주로 분류. SPAD 200 미반영 및 9천원대 매물 소화 과제.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['군공항', '호남', '반도체']</t>
+          <t>['데이터 센터', '양자컴퓨터', '매물 소화']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9590</v>
+        <v>9490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.48%</t>
+          <t>'+7.35%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>77242327930</v>
+        <v>78656966450</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18260</v>
+        <v>18360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.52%</t>
+          <t>'+5.09%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F6" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G6" t="n">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>136774457530</v>
+        <v>138076423215</v>
       </c>
       <c r="P6" t="n">
         <v>28800</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>반도체 테마 수혜 기대, 일본 및 호남 공장 관련 긍정적 전망, 글로벌 파운드리 연내 착공 뉴스.</t>
+          <t>반도체 테마 내 저평가 매력 및 공급망 확충, 메가 반도체 공장 수혜 기대감. 글로벌 파운드리 연내 착공 초기 핵심 고객 부각.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체', '수혜주', '파운드리']</t>
+          <t>['반도체 테마', '공급망', '파운드리']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10340</v>
+        <v>18830</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.13%</t>
+          <t>'+3.63%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>27.77</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9930</v>
+        <v>18170</v>
       </c>
       <c r="K7" t="n">
-        <v>10100</v>
+        <v>18340</v>
       </c>
       <c r="L7" t="n">
-        <v>11100</v>
+        <v>18990</v>
       </c>
       <c r="M7" t="n">
-        <v>9860</v>
+        <v>18110</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>27.82</v>
       </c>
       <c r="O7" t="n">
-        <v>29909555460</v>
+        <v>27745672230</v>
       </c>
       <c r="P7" t="n">
-        <v>19380</v>
+        <v>35350</v>
       </c>
       <c r="Q7" t="n">
-        <v>3200</v>
+        <v>17210</v>
       </c>
       <c r="R7" t="n">
-        <v>-140000</v>
+        <v>312000</v>
       </c>
       <c r="S7" t="n">
-        <v>-3000</v>
+        <v>106000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
+          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
+          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,18 +1108,18 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18810</v>
+        <v>10280</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1127,19 +1127,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H8" t="n">
-        <v>27.77</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18170</v>
+        <v>9930</v>
       </c>
       <c r="K8" t="n">
-        <v>18340</v>
+        <v>10100</v>
       </c>
       <c r="L8" t="n">
-        <v>18990</v>
+        <v>11100</v>
       </c>
       <c r="M8" t="n">
-        <v>18110</v>
+        <v>9860</v>
       </c>
       <c r="N8" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>27094016190</v>
+        <v>30099774910</v>
       </c>
       <c r="P8" t="n">
-        <v>35350</v>
+        <v>19380</v>
       </c>
       <c r="Q8" t="n">
-        <v>17210</v>
+        <v>3200</v>
       </c>
       <c r="R8" t="n">
-        <v>312000</v>
+        <v>-140000</v>
       </c>
       <c r="S8" t="n">
-        <v>106000</v>
+        <v>-3000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
+          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
+          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65200</v>
+        <v>65400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.00%</t>
+          <t>'+3.32%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" t="n">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="H9" t="n">
         <v>22.1</v>
@@ -1254,7 +1254,7 @@
         <v>22.11</v>
       </c>
       <c r="O9" t="n">
-        <v>74452891350</v>
+        <v>77008019150</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>원전 관련주로서 뉴스케일파워 상승 언급과 함께 3분기 매출 하회 및 신뢰도 저하에 대한 우려.</t>
+          <t>뉴스케일파워 등 타 원전주 상승 대비 부진에 대한 실망감 표출. 3분기 매출 하회 가능성 및 신뢰도 하락에 대한 우려. 일부 긍정적 전망도 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전주', '뉴스케일파워', '매출']</t>
+          <t>['원전주', '매출 하회', '신뢰도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,70 +1299,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13410</v>
+        <v>23900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.68%</t>
+          <t>'+3.02%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.21</v>
+        <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="H10" t="n">
-        <v>3.42</v>
+        <v>9.23</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13060</v>
+        <v>23200</v>
       </c>
       <c r="K10" t="n">
-        <v>13390</v>
+        <v>23250</v>
       </c>
       <c r="L10" t="n">
-        <v>13620</v>
+        <v>24250</v>
       </c>
       <c r="M10" t="n">
-        <v>12910</v>
+        <v>22900</v>
       </c>
       <c r="N10" t="n">
-        <v>3.21</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>32767881045</v>
+        <v>30899658725</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>24950</v>
       </c>
       <c r="Q10" t="n">
-        <v>1640</v>
+        <v>17910</v>
       </c>
       <c r="R10" t="n">
-        <v>-62000</v>
+        <v>435000</v>
       </c>
       <c r="S10" t="n">
-        <v>-11000</v>
+        <v>-20000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
+          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '미국장 반등']</t>
+          <t>['운항수익', '영업이익', 'SCFI']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>011200</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23750</v>
+        <v>215500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.37%</t>
+          <t>'+2.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>-0.18</v>
       </c>
       <c r="E11" t="n">
-        <v>49</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>505</v>
       </c>
       <c r="G11" t="n">
-        <v>245</v>
+        <v>1111</v>
       </c>
       <c r="H11" t="n">
-        <v>9.23</v>
+        <v>45.98</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,139 +1423,139 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>23200</v>
+        <v>210000</v>
       </c>
       <c r="K11" t="n">
-        <v>23250</v>
+        <v>215000</v>
       </c>
       <c r="L11" t="n">
-        <v>24250</v>
+        <v>217500</v>
       </c>
       <c r="M11" t="n">
-        <v>22900</v>
+        <v>210500</v>
       </c>
       <c r="N11" t="n">
-        <v>9.210000000000001</v>
+        <v>46.16</v>
       </c>
       <c r="O11" t="n">
-        <v>28603505275</v>
+        <v>1613094528750</v>
       </c>
       <c r="P11" t="n">
-        <v>24950</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>17910</v>
+        <v>94500</v>
       </c>
       <c r="R11" t="n">
-        <v>435000</v>
+        <v>-684000</v>
       </c>
       <c r="S11" t="n">
-        <v>-20000</v>
+        <v>-108000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
+          <t>정치적 이슈와 개인 투자자 손실에 대한 불만 토로. 일부 AI 관련 긍정적 언급도 있으나, 전반적으로 혼란스러운 심리가 지배적.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['운항수익', '영업이익', 'SCFI']</t>
+          <t>['정치', '주주 손실', 'AI']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>214500</v>
+        <v>13390</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.14%</t>
+          <t>'+2.53%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.18</v>
+        <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
-        <v>501</v>
+        <v>28</v>
       </c>
       <c r="G12" t="n">
-        <v>1148</v>
+        <v>169</v>
       </c>
       <c r="H12" t="n">
-        <v>45.98</v>
+        <v>3.42</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>210000</v>
+        <v>13060</v>
       </c>
       <c r="K12" t="n">
-        <v>215000</v>
+        <v>13390</v>
       </c>
       <c r="L12" t="n">
-        <v>217500</v>
+        <v>13620</v>
       </c>
       <c r="M12" t="n">
-        <v>210500</v>
+        <v>12910</v>
       </c>
       <c r="N12" t="n">
-        <v>46.16</v>
+        <v>3.21</v>
       </c>
       <c r="O12" t="n">
-        <v>1564943018500</v>
+        <v>33324215250</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>94500</v>
+        <v>1640</v>
       </c>
       <c r="R12" t="n">
-        <v>-684000</v>
+        <v>-62000</v>
       </c>
       <c r="S12" t="n">
-        <v>-108000</v>
+        <v>-11000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 이슈와 노조 관련 언급, 외인 매도량 분석, 유가 상승 우려 등 복합적인 부정적 전망.</t>
+          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['외인매도', '유가', '노조']</t>
+          <t>['광통신', '야간선물', '미국장 반등']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1289000</v>
+        <v>1291000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.14%</t>
+          <t>'+2.30%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>532</v>
+        <v>513</v>
       </c>
       <c r="G13" t="n">
-        <v>1246</v>
+        <v>1223</v>
       </c>
       <c r="H13" t="n">
         <v>48.85</v>
@@ -1622,7 +1622,7 @@
         <v>49.02</v>
       </c>
       <c r="O13" t="n">
-        <v>2730533873500</v>
+        <v>2800947392500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 부정적 언급, 외인 비중 축소 및 개미 투자자 매수세에 대한 회의적인 시각.</t>
+          <t>국가 경제 비상 사태에 대한 우려와 함께 개인 투자자의 반대매매, 외인 매도세에 대한 불만이 고조됨. 회장 및 경영진에 대한 비판적 언급 다수.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외인비중', '개미', '반대매매']</t>
+          <t>['경제 비상', '외인 매도', '반대매매']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,83 +1667,83 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>41350</v>
+        <v>14940</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.47%</t>
+          <t>'+1.84%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="F14" t="n">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
-        <v>796</v>
+        <v>146</v>
       </c>
       <c r="H14" t="n">
-        <v>12.97</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>40750</v>
+        <v>14670</v>
       </c>
       <c r="K14" t="n">
-        <v>40600</v>
+        <v>14800</v>
       </c>
       <c r="L14" t="n">
-        <v>41450</v>
+        <v>15270</v>
       </c>
       <c r="M14" t="n">
-        <v>40050</v>
+        <v>14800</v>
       </c>
       <c r="N14" t="n">
-        <v>12.84</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>7812397275</v>
+        <v>22044573950</v>
       </c>
       <c r="P14" t="n">
-        <v>69200</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>24150</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>15000</v>
+        <v>-92000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>HLB의 담관암 FDA 승인 관련 기대감과 함께 진양곤 회장의 IR 활동 및 외인 매수세 확인.</t>
+          <t>주가 조작 및 공매도에 대한 강한 의혹 제기. 경영진 및 금융 당국에 대한 불신과 함께 주주 연대의 필요성 강조. 200일선 회복 중요성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['HLB', 'FDA승인', '진양곤']</t>
+          <t>['주가 조작', '공매도', '주주 연대']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14880</v>
+        <v>41400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.43%</t>
+          <t>'+1.60%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="E15" t="n">
-        <v>104</v>
+        <v>205</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="G15" t="n">
-        <v>142</v>
+        <v>798</v>
       </c>
       <c r="H15" t="n">
-        <v>9.779999999999999</v>
+        <v>12.97</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14670</v>
+        <v>40750</v>
       </c>
       <c r="K15" t="n">
-        <v>14800</v>
+        <v>40600</v>
       </c>
       <c r="L15" t="n">
-        <v>15270</v>
+        <v>41500</v>
       </c>
       <c r="M15" t="n">
-        <v>14800</v>
+        <v>40050</v>
       </c>
       <c r="N15" t="n">
-        <v>9.710000000000001</v>
+        <v>12.84</v>
       </c>
       <c r="O15" t="n">
-        <v>21526973655</v>
+        <v>8320100675</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>69200</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>24150</v>
       </c>
       <c r="R15" t="n">
-        <v>-92000</v>
+        <v>15000</v>
       </c>
       <c r="S15" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 조작 의혹과 정치적 개입 비판, 공매도 관련 언급 등 강한 부정적 심리.</t>
+          <t>HLB의 담관암 FDA 승인 관련 기대감과 함께 진양곤 회장의 IR 활동 및 외인 매수세 확인.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '정치']</t>
+          <t>['HLB', 'FDA승인', '진양곤']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14930</v>
+        <v>14950</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.07%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F16" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G16" t="n">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="H16" t="n">
         <v>0.11</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>37949468880</v>
+        <v>38196546020</v>
       </c>
       <c r="P16" t="n">
         <v>30800</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>상장 사기 의혹, 경영진 비판, 거래량 및 시가총액 관련 부정적 평가.</t>
+          <t>상장 사기 의혹 및 경영진(김임준) 무능력에 대한 강한 비판. 코넥스 시절 대비 부진한 주가 흐름과 수급 불안정성 지적.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['상장사기', '경영진', '시가총액']</t>
+          <t>['상장 사기', '경영진 비판', '수급 불안정']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19990</v>
+        <v>20000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.66%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2.5</v>
       </c>
       <c r="E17" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G17" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="H17" t="n">
         <v>4.28</v>
@@ -1990,7 +1990,7 @@
         <v>1.78</v>
       </c>
       <c r="O17" t="n">
-        <v>33724728110</v>
+        <v>34119698725</v>
       </c>
       <c r="P17" t="n">
         <v>22450</v>
@@ -2039,27 +2039,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27200</v>
+        <v>27300</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.64%</t>
+          <t>'-7.30%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F18" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="H18" t="n">
-        <v>53.42</v>
+        <v>53.43</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2076,13 +2076,13 @@
         <v>29600</v>
       </c>
       <c r="M18" t="n">
-        <v>27150</v>
+        <v>27100</v>
       </c>
       <c r="N18" t="n">
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>85254968975</v>
+        <v>89927793775</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>

--- a/data/trending_integrated_20261016_11.xlsx
+++ b/data/trending_integrated_20261016_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8660</v>
+        <v>8740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.12%</t>
+          <t>'+22.24%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G2" t="n">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -610,7 +610,7 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>155039289960</v>
+        <v>157656451020</v>
       </c>
       <c r="P2" t="n">
         <v>8920</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>인수합병 및 편입 기대감으로 인한 강한 상승세. 텐버거 가능성 등 과감한 목표가 제시. 악성매물 소화 및 신고가 경신 기대감 고조.</t>
+          <t>인수합병 기대감과 함께 텐버거 가능성, 신고가 경신에 대한 긍정적인 전망이 제시됨.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7800</v>
+        <v>7910</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.72%</t>
+          <t>'+20.40%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G3" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>65737554835</v>
+        <v>66175741895</v>
       </c>
       <c r="P3" t="n">
         <v>10300</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8330</v>
+        <v>8260</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.50%</t>
+          <t>'+15.52%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>40943864705</v>
+        <v>43263183660</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9490</v>
+        <v>9590</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.35%</t>
+          <t>'+8.48%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>78656966450</v>
+        <v>79456936710</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18360</v>
+        <v>18300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.09%</t>
+          <t>'+4.75%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F6" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G6" t="n">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>138076423215</v>
+        <v>139075197840</v>
       </c>
       <c r="P6" t="n">
         <v>28800</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>반도체 테마 내 저평가 매력 및 공급망 확충, 메가 반도체 공장 수혜 기대감. 글로벌 파운드리 연내 착공 초기 핵심 고객 부각.</t>
+          <t>반도체 테마 수혜주로서 공급망 확충 및 글로벌 파운드리 착공 뉴스가 호재로 작용할 전망이며, 급등 기대감도 있음.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체 테마', '공급망', '파운드리']</t>
+          <t>['반도체', '공급망', '파운드리']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18830</v>
+        <v>10350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.63%</t>
+          <t>'+4.23%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="H7" t="n">
-        <v>27.77</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18170</v>
+        <v>9930</v>
       </c>
       <c r="K7" t="n">
-        <v>18340</v>
+        <v>10100</v>
       </c>
       <c r="L7" t="n">
-        <v>18990</v>
+        <v>11100</v>
       </c>
       <c r="M7" t="n">
-        <v>18110</v>
+        <v>9860</v>
       </c>
       <c r="N7" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>27745672230</v>
+        <v>30275068125</v>
       </c>
       <c r="P7" t="n">
-        <v>35350</v>
+        <v>19380</v>
       </c>
       <c r="Q7" t="n">
-        <v>17210</v>
+        <v>3200</v>
       </c>
       <c r="R7" t="n">
-        <v>312000</v>
+        <v>-140000</v>
       </c>
       <c r="S7" t="n">
-        <v>106000</v>
+        <v>-3000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
+          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
+          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10280</v>
+        <v>18930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.52%</t>
+          <t>'+4.18%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>27.77</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9930</v>
+        <v>18170</v>
       </c>
       <c r="K8" t="n">
-        <v>10100</v>
+        <v>18340</v>
       </c>
       <c r="L8" t="n">
-        <v>11100</v>
+        <v>18990</v>
       </c>
       <c r="M8" t="n">
-        <v>9860</v>
+        <v>18110</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>27.82</v>
       </c>
       <c r="O8" t="n">
-        <v>30099774910</v>
+        <v>28972491430</v>
       </c>
       <c r="P8" t="n">
-        <v>19380</v>
+        <v>35350</v>
       </c>
       <c r="Q8" t="n">
-        <v>3200</v>
+        <v>17210</v>
       </c>
       <c r="R8" t="n">
-        <v>-140000</v>
+        <v>312000</v>
       </c>
       <c r="S8" t="n">
-        <v>-3000</v>
+        <v>106000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
+          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
+          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65400</v>
+        <v>65500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.32%</t>
+          <t>'+3.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F9" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G9" t="n">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="H9" t="n">
         <v>22.1</v>
@@ -1254,7 +1254,7 @@
         <v>22.11</v>
       </c>
       <c r="O9" t="n">
-        <v>77008019150</v>
+        <v>78076438400</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>뉴스케일파워 등 타 원전주 상승 대비 부진에 대한 실망감 표출. 3분기 매출 하회 가능성 및 신뢰도 하락에 대한 우려. 일부 긍정적 전망도 존재.</t>
+          <t>원전 관련주로서의 기대와 함께 매출 하회, 외국계 증권사 매도 등의 부정적인 요인이 언급됨.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전주', '매출 하회', '신뢰도']</t>
+          <t>['원전', '매출', '외국계 증권사']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,70 +1299,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23900</v>
+        <v>13440</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.02%</t>
+          <t>'+2.91%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.02</v>
+        <v>0.21</v>
       </c>
       <c r="E10" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>249</v>
+        <v>167</v>
       </c>
       <c r="H10" t="n">
-        <v>9.23</v>
+        <v>3.42</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>23200</v>
+        <v>13060</v>
       </c>
       <c r="K10" t="n">
-        <v>23250</v>
+        <v>13390</v>
       </c>
       <c r="L10" t="n">
-        <v>24250</v>
+        <v>13620</v>
       </c>
       <c r="M10" t="n">
-        <v>22900</v>
+        <v>12910</v>
       </c>
       <c r="N10" t="n">
-        <v>9.210000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="O10" t="n">
-        <v>30899658725</v>
+        <v>33778555270</v>
       </c>
       <c r="P10" t="n">
-        <v>24950</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>17910</v>
+        <v>1640</v>
       </c>
       <c r="R10" t="n">
-        <v>435000</v>
+        <v>-62000</v>
       </c>
       <c r="S10" t="n">
-        <v>-20000</v>
+        <v>-11000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
+          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['운항수익', '영업이익', 'SCFI']</t>
+          <t>['광통신', '야간선물', '미국장 반등']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>215500</v>
+        <v>23850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.62%</t>
+          <t>'+2.80%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.18</v>
+        <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>505</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>1111</v>
+        <v>270</v>
       </c>
       <c r="H11" t="n">
-        <v>45.98</v>
+        <v>9.23</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,139 +1423,139 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>210000</v>
+        <v>23200</v>
       </c>
       <c r="K11" t="n">
-        <v>215000</v>
+        <v>23250</v>
       </c>
       <c r="L11" t="n">
-        <v>217500</v>
+        <v>24250</v>
       </c>
       <c r="M11" t="n">
-        <v>210500</v>
+        <v>22900</v>
       </c>
       <c r="N11" t="n">
-        <v>46.16</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>1613094528750</v>
+        <v>32078521725</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>24950</v>
       </c>
       <c r="Q11" t="n">
-        <v>94500</v>
+        <v>17910</v>
       </c>
       <c r="R11" t="n">
-        <v>-684000</v>
+        <v>435000</v>
       </c>
       <c r="S11" t="n">
-        <v>-108000</v>
+        <v>-20000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 개인 투자자 손실에 대한 불만 토로. 일부 AI 관련 긍정적 언급도 있으나, 전반적으로 혼란스러운 심리가 지배적.</t>
+          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['정치', '주주 손실', 'AI']</t>
+          <t>['운항수익', '영업이익', 'SCFI']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>011200</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13390</v>
+        <v>215500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.53%</t>
+          <t>'+2.62%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="E12" t="n">
-        <v>43</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>507</v>
       </c>
       <c r="G12" t="n">
-        <v>169</v>
+        <v>1091</v>
       </c>
       <c r="H12" t="n">
-        <v>3.42</v>
+        <v>45.98</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13060</v>
+        <v>210000</v>
       </c>
       <c r="K12" t="n">
-        <v>13390</v>
+        <v>215000</v>
       </c>
       <c r="L12" t="n">
-        <v>13620</v>
+        <v>217500</v>
       </c>
       <c r="M12" t="n">
-        <v>12910</v>
+        <v>210500</v>
       </c>
       <c r="N12" t="n">
-        <v>3.21</v>
+        <v>46.16</v>
       </c>
       <c r="O12" t="n">
-        <v>33324215250</v>
+        <v>1674269821500</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>1640</v>
+        <v>94500</v>
       </c>
       <c r="R12" t="n">
-        <v>-62000</v>
+        <v>-684000</v>
       </c>
       <c r="S12" t="n">
-        <v>-11000</v>
+        <v>-108000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
+          <t>정치적 논쟁과 부정적인 시장 전망이 혼재하며, 투자자들의 멘탈에 대한 언급이 있음.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '미국장 반등']</t>
+          <t>['정치', '시장 전망', '투자자 멘탈']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,43 +1563,43 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1291000</v>
+        <v>15010</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.30%</t>
+          <t>'+2.32%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>117</v>
       </c>
       <c r="F13" t="n">
-        <v>513</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>1223</v>
+        <v>216</v>
       </c>
       <c r="H13" t="n">
-        <v>48.85</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1262000</v>
+        <v>14670</v>
       </c>
       <c r="K13" t="n">
-        <v>1290000</v>
+        <v>14800</v>
       </c>
       <c r="L13" t="n">
-        <v>1308000</v>
+        <v>15270</v>
       </c>
       <c r="M13" t="n">
-        <v>1247000</v>
+        <v>14800</v>
       </c>
       <c r="N13" t="n">
-        <v>49.02</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>2800947392500</v>
+        <v>23038641360</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>420500</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-448000</v>
+        <v>-92000</v>
       </c>
       <c r="S13" t="n">
-        <v>-27000</v>
+        <v>7000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국가 경제 비상 사태에 대한 우려와 함께 개인 투자자의 반대매매, 외인 매도세에 대한 불만이 고조됨. 회장 및 경영진에 대한 비판적 언급 다수.</t>
+          <t>주가 조작 의혹 및 금감원, 이재명 대통령에 대한 강한 비판과 함께 마진콜, 대차 해지 중요성이 언급됨.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['경제 비상', '외인 매도', '반대매매']</t>
+          <t>['주가 조작', '금감원', '마진콜']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14940</v>
+        <v>1289000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.84%</t>
+          <t>'+2.14%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.17</v>
       </c>
       <c r="E14" t="n">
-        <v>110</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>514</v>
       </c>
       <c r="G14" t="n">
-        <v>146</v>
+        <v>1177</v>
       </c>
       <c r="H14" t="n">
-        <v>9.779999999999999</v>
+        <v>48.85</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,47 +1699,47 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14670</v>
+        <v>1262000</v>
       </c>
       <c r="K14" t="n">
-        <v>14800</v>
+        <v>1290000</v>
       </c>
       <c r="L14" t="n">
-        <v>15270</v>
+        <v>1308000</v>
       </c>
       <c r="M14" t="n">
-        <v>14800</v>
+        <v>1247000</v>
       </c>
       <c r="N14" t="n">
-        <v>9.710000000000001</v>
+        <v>49.02</v>
       </c>
       <c r="O14" t="n">
-        <v>22044573950</v>
+        <v>2847668363000</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>420500</v>
       </c>
       <c r="R14" t="n">
-        <v>-92000</v>
+        <v>-448000</v>
       </c>
       <c r="S14" t="n">
-        <v>7000</v>
+        <v>-27000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도에 대한 강한 의혹 제기. 경영진 및 금융 당국에 대한 불신과 함께 주주 연대의 필요성 강조. 200일선 회복 중요성 언급.</t>
+          <t>국가적 비상사태 언급과 함께 외인 매도세, 주가 반등의 미약함에 대한 불만이 제기됨.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '주주 연대']</t>
+          <t>['외인 매도', '주가 반등', '국가 비상사태']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41400</v>
+        <v>41500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.60%</t>
+          <t>'+1.84%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.13</v>
       </c>
       <c r="E15" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F15" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G15" t="n">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="H15" t="n">
         <v>12.97</v>
@@ -1797,7 +1797,7 @@
         <v>40600</v>
       </c>
       <c r="L15" t="n">
-        <v>41500</v>
+        <v>41600</v>
       </c>
       <c r="M15" t="n">
         <v>40050</v>
@@ -1806,7 +1806,7 @@
         <v>12.84</v>
       </c>
       <c r="O15" t="n">
-        <v>8320100675</v>
+        <v>8571838475</v>
       </c>
       <c r="P15" t="n">
         <v>69200</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>HLB의 담관암 FDA 승인 관련 기대감과 함께 진양곤 회장의 IR 활동 및 외인 매수세 확인.</t>
+          <t>담관암 FDA 승인 기대감과 함께 외인 매수세 유입이 확인되었으나, 진양곤 회장 등 변수에 대한 불안감도 존재함.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['HLB', 'FDA승인', '진양곤']</t>
+          <t>['FDA 승인', '외인 매수', '담관암']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14950</v>
+        <v>14910</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'-0.20%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="F16" t="n">
         <v>67</v>
       </c>
       <c r="G16" t="n">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="H16" t="n">
         <v>0.11</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>38196546020</v>
+        <v>38422483430</v>
       </c>
       <c r="P16" t="n">
         <v>30800</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>상장 사기 의혹 및 경영진(김임준) 무능력에 대한 강한 비판. 코넥스 시절 대비 부진한 주가 흐름과 수급 불안정성 지적.</t>
+          <t>상장 사기 의혹과 함께 금감원, 대표 사퇴 요구 등 강한 불만이 제기되며, 단일 계좌를 통한 물량 쓸이에 대한 지적이 있음.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['상장 사기', '경영진 비판', '수급 불안정']</t>
+          <t>['상장 사기', '금감원', '단일 계좌']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20000</v>
+        <v>19900</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-4.10%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2.5</v>
       </c>
       <c r="E17" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G17" t="n">
         <v>186</v>
@@ -1990,7 +1990,7 @@
         <v>1.78</v>
       </c>
       <c r="O17" t="n">
-        <v>34119698725</v>
+        <v>34600213545</v>
       </c>
       <c r="P17" t="n">
         <v>22450</v>
@@ -2039,27 +2039,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27300</v>
+        <v>27200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.30%</t>
+          <t>'-7.64%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F18" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G18" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="H18" t="n">
-        <v>53.43</v>
+        <v>53.44</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>89927793775</v>
+        <v>94102726925</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>

--- a/data/trending_integrated_20261016_11.xlsx
+++ b/data/trending_integrated_20261016_11.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8740</v>
+        <v>8890</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.24%</t>
+          <t>'+24.34%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,7 +581,7 @@
         <v>118</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G2" t="n">
         <v>212</v>
@@ -601,7 +601,7 @@
         <v>7430</v>
       </c>
       <c r="L2" t="n">
-        <v>8920</v>
+        <v>8930</v>
       </c>
       <c r="M2" t="n">
         <v>7300</v>
@@ -610,10 +610,10 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>157656451020</v>
+        <v>163989148740</v>
       </c>
       <c r="P2" t="n">
-        <v>8920</v>
+        <v>8930</v>
       </c>
       <c r="Q2" t="n">
         <v>2270</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>인수합병 기대감과 함께 텐버거 가능성, 신고가 경신에 대한 긍정적인 전망이 제시됨.</t>
+          <t>인수합병 기대감 및 텐버거 가능성에 대한 긍정적 전망과 함께 악성 매물 소화 과정 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['인수합병', '텐버거', '신고가']</t>
+          <t>['인수합병', '텐버거']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7910</v>
+        <v>7960</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.40%</t>
+          <t>'+21.16%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>66175741895</v>
+        <v>66966417050</v>
       </c>
       <c r="P3" t="n">
         <v>10300</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>군공항 이전 이슈와 호남 반도체 관련 뉴스로 인한 급등세. 신고가 경신 시 8만원 돌파 가능성 언급. 투기성 수급 유입 확인.</t>
+          <t>군공항 이전 이슈와 관련된 기대감 및 정치권 언급, 신고가 돌파 시 추가 상승 가능성 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['군공항 이전', '호남 반도체', '투기']</t>
+          <t>['군공항 이전', '신고가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8260</v>
+        <v>8270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.52%</t>
+          <t>'+15.66%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>43263183660</v>
+        <v>44895714530</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9590</v>
+        <v>9620</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.48%</t>
+          <t>'+8.82%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>79456936710</v>
+        <v>80078669355</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18300</v>
+        <v>18400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.75%</t>
+          <t>'+5.32%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F6" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>139075197840</v>
+        <v>139723509055</v>
       </c>
       <c r="P6" t="n">
         <v>28800</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10350</v>
+        <v>10370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.23%</t>
+          <t>'+4.43%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
         <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>30275068125</v>
+        <v>30364120585</v>
       </c>
       <c r="P7" t="n">
         <v>19380</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18930</v>
+        <v>18940</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.18%</t>
+          <t>'+4.24%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F8" t="n">
         <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H8" t="n">
         <v>27.77</v>
@@ -1162,7 +1162,7 @@
         <v>27.82</v>
       </c>
       <c r="O8" t="n">
-        <v>28972491430</v>
+        <v>29944694805</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65500</v>
+        <v>65700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.48%</t>
+          <t>'+3.79%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G9" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H9" t="n">
         <v>22.1</v>
@@ -1254,7 +1254,7 @@
         <v>22.11</v>
       </c>
       <c r="O9" t="n">
-        <v>78076438400</v>
+        <v>80226262850</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1299,70 +1299,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13440</v>
+        <v>216500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.91%</t>
+          <t>'+3.10%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>497</v>
       </c>
       <c r="G10" t="n">
-        <v>167</v>
+        <v>1080</v>
       </c>
       <c r="H10" t="n">
-        <v>3.42</v>
+        <v>45.98</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13060</v>
+        <v>210000</v>
       </c>
       <c r="K10" t="n">
-        <v>13390</v>
+        <v>215000</v>
       </c>
       <c r="L10" t="n">
-        <v>13620</v>
+        <v>217500</v>
       </c>
       <c r="M10" t="n">
-        <v>12910</v>
+        <v>210500</v>
       </c>
       <c r="N10" t="n">
-        <v>3.21</v>
+        <v>46.16</v>
       </c>
       <c r="O10" t="n">
-        <v>33778555270</v>
+        <v>1704551613750</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>1640</v>
+        <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>-62000</v>
+        <v>-684000</v>
       </c>
       <c r="S10" t="n">
-        <v>-11000</v>
+        <v>-108000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
+          <t>정치적 이슈와 유가 변동성에 대한 언급이 주를 이루며, 외인 수급에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '미국장 반등']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,82 +1379,82 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23850</v>
+        <v>13460</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.80%</t>
+          <t>'+3.06%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>0.21</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
-        <v>270</v>
+        <v>175</v>
       </c>
       <c r="H11" t="n">
-        <v>9.23</v>
+        <v>3.42</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>23200</v>
+        <v>13060</v>
       </c>
       <c r="K11" t="n">
-        <v>23250</v>
+        <v>13390</v>
       </c>
       <c r="L11" t="n">
-        <v>24250</v>
+        <v>13620</v>
       </c>
       <c r="M11" t="n">
-        <v>22900</v>
+        <v>12910</v>
       </c>
       <c r="N11" t="n">
-        <v>9.210000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="O11" t="n">
-        <v>32078521725</v>
+        <v>34084770880</v>
       </c>
       <c r="P11" t="n">
-        <v>24950</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>17910</v>
+        <v>1640</v>
       </c>
       <c r="R11" t="n">
-        <v>435000</v>
+        <v>-62000</v>
       </c>
       <c r="S11" t="n">
-        <v>-20000</v>
+        <v>-11000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
+          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['운항수익', '영업이익', 'SCFI']</t>
+          <t>['광통신', '야간선물', '미국장 반등']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>215500</v>
+        <v>23850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.62%</t>
+          <t>'+2.80%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.18</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>507</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>1091</v>
+        <v>307</v>
       </c>
       <c r="H12" t="n">
-        <v>45.98</v>
+        <v>9.23</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,60 +1515,60 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>210000</v>
+        <v>23200</v>
       </c>
       <c r="K12" t="n">
-        <v>215000</v>
+        <v>23250</v>
       </c>
       <c r="L12" t="n">
-        <v>217500</v>
+        <v>24250</v>
       </c>
       <c r="M12" t="n">
-        <v>210500</v>
+        <v>22900</v>
       </c>
       <c r="N12" t="n">
-        <v>46.16</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>1674269821500</v>
+        <v>32670594825</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>24950</v>
       </c>
       <c r="Q12" t="n">
-        <v>94500</v>
+        <v>17910</v>
       </c>
       <c r="R12" t="n">
-        <v>-684000</v>
+        <v>435000</v>
       </c>
       <c r="S12" t="n">
-        <v>-108000</v>
+        <v>-20000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 논쟁과 부정적인 시장 전망이 혼재하며, 투자자들의 멘탈에 대한 언급이 있음.</t>
+          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정치', '시장 전망', '투자자 멘탈']</t>
+          <t>['운항수익', '영업이익', 'SCFI']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>011200</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15010</v>
+        <v>15020</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.32%</t>
+          <t>'+2.39%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="H13" t="n">
         <v>9.779999999999999</v>
@@ -1622,7 +1622,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>23038641360</v>
+        <v>23760558070</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 금감원, 이재명 대통령에 대한 강한 비판과 함께 마진콜, 대차 해지 중요성이 언급됨.</t>
+          <t>주가 조작 및 금감원 사모펀드 점검에 대한 반복적인 언급과 함께 정치권에 대한 비판.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가 조작', '금감원', '마진콜']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1289000</v>
+        <v>1292000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.14%</t>
+          <t>'+2.38%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="G14" t="n">
-        <v>1177</v>
+        <v>1163</v>
       </c>
       <c r="H14" t="n">
         <v>48.85</v>
@@ -1714,7 +1714,7 @@
         <v>49.02</v>
       </c>
       <c r="O14" t="n">
-        <v>2847668363000</v>
+        <v>2897734553500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>국가적 비상사태 언급과 함께 외인 매도세, 주가 반등의 미약함에 대한 불만이 제기됨.</t>
+          <t>국가적 위기 상황 및 외국인 매도세 언급과 함께 주가 반등에 대한 회의적인 시각.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외인 매도', '주가 반등', '국가 비상사태']</t>
+          <t>['외국인 매도', '국가 위기']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41500</v>
+        <v>41550</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.84%</t>
+          <t>'+1.96%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.13</v>
       </c>
       <c r="E15" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F15" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G15" t="n">
-        <v>819</v>
+        <v>829</v>
       </c>
       <c r="H15" t="n">
         <v>12.97</v>
@@ -1797,7 +1797,7 @@
         <v>40600</v>
       </c>
       <c r="L15" t="n">
-        <v>41600</v>
+        <v>41650</v>
       </c>
       <c r="M15" t="n">
         <v>40050</v>
@@ -1806,7 +1806,7 @@
         <v>12.84</v>
       </c>
       <c r="O15" t="n">
-        <v>8571838475</v>
+        <v>9106815150</v>
       </c>
       <c r="P15" t="n">
         <v>69200</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14910</v>
+        <v>15030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.20%</t>
+          <t>'+0.60%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="F16" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G16" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="H16" t="n">
         <v>0.11</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>38422483430</v>
+        <v>38901977810</v>
       </c>
       <c r="P16" t="n">
         <v>30800</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>상장 사기 의혹과 함께 금감원, 대표 사퇴 요구 등 강한 불만이 제기되며, 단일 계좌를 통한 물량 쓸이에 대한 지적이 있음.</t>
+          <t>상장 사기 의혹 및 높은 공모가에 대한 비판과 함께 경영진 사퇴 요구.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['상장 사기', '금감원', '단일 계좌']</t>
+          <t>['상장 사기', '공모가']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19900</v>
+        <v>19910</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.10%</t>
+          <t>'-4.05%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2.5</v>
       </c>
       <c r="E17" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F17" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G17" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="H17" t="n">
         <v>4.28</v>
@@ -1990,7 +1990,7 @@
         <v>1.78</v>
       </c>
       <c r="O17" t="n">
-        <v>34600213545</v>
+        <v>35149780600</v>
       </c>
       <c r="P17" t="n">
         <v>22450</v>
@@ -2039,27 +2039,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27200</v>
+        <v>27350</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.64%</t>
+          <t>'-7.13%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F18" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G18" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="H18" t="n">
-        <v>53.44</v>
+        <v>53.46</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>94102726925</v>
+        <v>96384128575</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 발표 후 외국인 매도 시작 및 주가 급락. 투자 심리 악화.</t>
+          <t>실적 발표 후 외국인 매도세와 함께 주가 하락에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적 발표', '외국인 매도', '주가 급락']</t>
+          <t>['외국인 매도', '실적 발표']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">

--- a/data/trending_integrated_20261016_11.xlsx
+++ b/data/trending_integrated_20261016_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8890</v>
+        <v>8815</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+24.34%</t>
+          <t>'+23.29%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="F2" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G2" t="n">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -601,7 +601,7 @@
         <v>7430</v>
       </c>
       <c r="L2" t="n">
-        <v>8930</v>
+        <v>8970</v>
       </c>
       <c r="M2" t="n">
         <v>7300</v>
@@ -610,10 +610,10 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>163989148740</v>
+        <v>170630141555</v>
       </c>
       <c r="P2" t="n">
-        <v>8930</v>
+        <v>8970</v>
       </c>
       <c r="Q2" t="n">
         <v>2270</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>인수합병 기대감 및 텐버거 가능성에 대한 긍정적 전망과 함께 악성 매물 소화 과정 언급.</t>
+          <t>인수합병 및 텐버거 가능성 언급, 일부 악성 매물 소화 과정으로 해석되며 긍정적인 기대감이 나타남.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['인수합병', '텐버거']</t>
+          <t>['인수합병', '텐버거', '매물 소화']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7960</v>
+        <v>7860</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.16%</t>
+          <t>'+19.63%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F3" t="n">
         <v>58</v>
       </c>
       <c r="G3" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>66966417050</v>
+        <v>67793775335</v>
       </c>
       <c r="P3" t="n">
         <v>10300</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>군공항 이전 이슈와 관련된 기대감 및 정치권 언급, 신고가 돌파 시 추가 상승 가능성 제시.</t>
+          <t>군공항 이전 관련 언급과 함께 신고가 돌파 및 8만원 가능성 등 상승 기대감이 존재하나, 투기 과열 종목 지정 등 변동성 우려도 있음.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['군공항 이전', '신고가']</t>
+          <t>['군공항', '신고가', '투기 과열']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8270</v>
+        <v>8280</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.66%</t>
+          <t>'+15.80%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>44895714530</v>
+        <v>45940109430</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9620</v>
+        <v>9690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.82%</t>
+          <t>'+9.62%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>80078669355</v>
+        <v>80956386315</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18400</v>
+        <v>18370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.32%</t>
+          <t>'+5.15%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F6" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G6" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>139723509055</v>
+        <v>140447920855</v>
       </c>
       <c r="P6" t="n">
         <v>28800</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>반도체 테마 수혜주로서 공급망 확충 및 글로벌 파운드리 착공 뉴스가 호재로 작용할 전망이며, 급등 기대감도 있음.</t>
+          <t>반도체 공장 수혜주로 언급되며 글로벌 파운드리 연내 착공 관련 뉴스가 호재로 작용할 수 있다는 전망이 있으나, 단일 계좌로 인한 투자 주의가 언급됨.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체', '공급망', '파운드리']</t>
+          <t>['반도체', '공장', '수혜주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F7" t="n">
         <v>27</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>30364120585</v>
+        <v>30521866975</v>
       </c>
       <c r="P7" t="n">
         <v>19380</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18940</v>
+        <v>18930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.24%</t>
+          <t>'+4.18%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H8" t="n">
         <v>27.77</v>
@@ -1162,7 +1162,7 @@
         <v>27.82</v>
       </c>
       <c r="O8" t="n">
-        <v>29944694805</v>
+        <v>30577374370</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65700</v>
+        <v>23900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.79%</t>
+          <t>'+3.02%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>122</v>
+        <v>56</v>
       </c>
       <c r="F9" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="G9" t="n">
-        <v>367</v>
+        <v>316</v>
       </c>
       <c r="H9" t="n">
-        <v>22.1</v>
+        <v>9.23</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,130 +1239,130 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>63300</v>
+        <v>23200</v>
       </c>
       <c r="K9" t="n">
-        <v>63900</v>
+        <v>23250</v>
       </c>
       <c r="L9" t="n">
-        <v>65700</v>
+        <v>24250</v>
       </c>
       <c r="M9" t="n">
-        <v>63500</v>
+        <v>22900</v>
       </c>
       <c r="N9" t="n">
-        <v>22.11</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>80226262850</v>
+        <v>33304624675</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>24950</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>17910</v>
       </c>
       <c r="R9" t="n">
-        <v>50000</v>
+        <v>435000</v>
       </c>
       <c r="S9" t="n">
-        <v>-24000</v>
+        <v>-20000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>원전 관련주로서의 기대와 함께 매출 하회, 외국계 증권사 매도 등의 부정적인 요인이 언급됨.</t>
+          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', '매출', '외국계 증권사']</t>
+          <t>['운항수익', '영업이익', 'SCFI']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>011200</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>216500</v>
+        <v>13440</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.10%</t>
+          <t>'+2.91%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.18</v>
+        <v>0.21</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>46</v>
       </c>
       <c r="F10" t="n">
-        <v>497</v>
+        <v>29</v>
       </c>
       <c r="G10" t="n">
-        <v>1080</v>
+        <v>174</v>
       </c>
       <c r="H10" t="n">
-        <v>45.98</v>
+        <v>3.42</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>210000</v>
+        <v>13060</v>
       </c>
       <c r="K10" t="n">
-        <v>215000</v>
+        <v>13390</v>
       </c>
       <c r="L10" t="n">
-        <v>217500</v>
+        <v>13620</v>
       </c>
       <c r="M10" t="n">
-        <v>210500</v>
+        <v>12910</v>
       </c>
       <c r="N10" t="n">
-        <v>46.16</v>
+        <v>3.21</v>
       </c>
       <c r="O10" t="n">
-        <v>1704551613750</v>
+        <v>34560875790</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>1640</v>
       </c>
       <c r="R10" t="n">
-        <v>-684000</v>
+        <v>-62000</v>
       </c>
       <c r="S10" t="n">
-        <v>-108000</v>
+        <v>-11000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈와 유가 변동성에 대한 언급이 주를 이루며, 외인 수급에 대한 부정적 전망.</t>
+          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['광통신', '야간선물', '미국장 반등']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,82 +1379,82 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13460</v>
+        <v>216000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.06%</t>
+          <t>'+2.86%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="E11" t="n">
-        <v>47</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>498</v>
       </c>
       <c r="G11" t="n">
-        <v>175</v>
+        <v>1056</v>
       </c>
       <c r="H11" t="n">
-        <v>3.42</v>
+        <v>45.98</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13060</v>
+        <v>210000</v>
       </c>
       <c r="K11" t="n">
-        <v>13390</v>
+        <v>215000</v>
       </c>
       <c r="L11" t="n">
-        <v>13620</v>
+        <v>217500</v>
       </c>
       <c r="M11" t="n">
-        <v>12910</v>
+        <v>210500</v>
       </c>
       <c r="N11" t="n">
-        <v>3.21</v>
+        <v>46.16</v>
       </c>
       <c r="O11" t="n">
-        <v>34084770880</v>
+        <v>1755553139250</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>1640</v>
+        <v>94500</v>
       </c>
       <c r="R11" t="n">
-        <v>-62000</v>
+        <v>-684000</v>
       </c>
       <c r="S11" t="n">
-        <v>-11000</v>
+        <v>-108000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
+          <t>정치 관련 언급이 주를 이루며, 주가와 관련된 구체적인 분석이나 근거는 부족함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '미국장 반등']</t>
+          <t>['정치', '주가', '외인']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,43 +1471,43 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23850</v>
+        <v>15040</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.80%</t>
+          <t>'+2.52%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>307</v>
+        <v>248</v>
       </c>
       <c r="H12" t="n">
-        <v>9.23</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,91 +1515,91 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>23200</v>
+        <v>14670</v>
       </c>
       <c r="K12" t="n">
-        <v>23250</v>
+        <v>14800</v>
       </c>
       <c r="L12" t="n">
-        <v>24250</v>
+        <v>15270</v>
       </c>
       <c r="M12" t="n">
-        <v>22900</v>
+        <v>14800</v>
       </c>
       <c r="N12" t="n">
-        <v>9.210000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>32670594825</v>
+        <v>24439131915</v>
       </c>
       <c r="P12" t="n">
-        <v>24950</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>17910</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>435000</v>
+        <v>-92000</v>
       </c>
       <c r="S12" t="n">
-        <v>-20000</v>
+        <v>7000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
+          <t>주가 조작 및 정부 관련 비판적인 언급이 반복되며, 구체적인 사업 내용 분석이나 긍정적인 전망은 미미함.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['운항수익', '영업이익', 'SCFI']</t>
+          <t>['주가 조작', '정부', '금감원']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15020</v>
+        <v>1290000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.39%</t>
+          <t>'+2.22%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.17</v>
       </c>
       <c r="E13" t="n">
-        <v>124</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>516</v>
       </c>
       <c r="G13" t="n">
-        <v>232</v>
+        <v>1150</v>
       </c>
       <c r="H13" t="n">
-        <v>9.779999999999999</v>
+        <v>48.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14670</v>
+        <v>1262000</v>
       </c>
       <c r="K13" t="n">
-        <v>14800</v>
+        <v>1290000</v>
       </c>
       <c r="L13" t="n">
-        <v>15270</v>
+        <v>1308000</v>
       </c>
       <c r="M13" t="n">
-        <v>14800</v>
+        <v>1247000</v>
       </c>
       <c r="N13" t="n">
-        <v>9.710000000000001</v>
+        <v>49.02</v>
       </c>
       <c r="O13" t="n">
-        <v>23760558070</v>
+        <v>2949434039000</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>420500</v>
       </c>
       <c r="R13" t="n">
-        <v>-92000</v>
+        <v>-448000</v>
       </c>
       <c r="S13" t="n">
-        <v>7000</v>
+        <v>-27000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 조작 및 금감원 사모펀드 점검에 대한 반복적인 언급과 함께 정치권에 대한 비판.</t>
+          <t>외인 매도세와 전저점 이탈 우려, 반등 동력 부족 등 부정적인 전망이 우세하며, 일부 정치적 언급 포함.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['외인', '전저점', '반등']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1292000</v>
+        <v>41600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.38%</t>
+          <t>'+2.09%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.17</v>
+        <v>0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>217</v>
       </c>
       <c r="F14" t="n">
-        <v>520</v>
+        <v>120</v>
       </c>
       <c r="G14" t="n">
-        <v>1163</v>
+        <v>843</v>
       </c>
       <c r="H14" t="n">
-        <v>48.85</v>
+        <v>12.97</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1262000</v>
+        <v>40750</v>
       </c>
       <c r="K14" t="n">
-        <v>1290000</v>
+        <v>40600</v>
       </c>
       <c r="L14" t="n">
-        <v>1308000</v>
+        <v>41650</v>
       </c>
       <c r="M14" t="n">
-        <v>1247000</v>
+        <v>40050</v>
       </c>
       <c r="N14" t="n">
-        <v>49.02</v>
+        <v>12.84</v>
       </c>
       <c r="O14" t="n">
-        <v>2897734553500</v>
+        <v>9334733425</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>69200</v>
       </c>
       <c r="Q14" t="n">
-        <v>420500</v>
+        <v>24150</v>
       </c>
       <c r="R14" t="n">
-        <v>-448000</v>
+        <v>15000</v>
       </c>
       <c r="S14" t="n">
-        <v>-27000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>국가적 위기 상황 및 외국인 매도세 언급과 함께 주가 반등에 대한 회의적인 시각.</t>
+          <t>FDA 승인 관련 기대감과 함께 IR 발표, 외국인 매수세 등 긍정적인 요소가 언급되나, 일부 불안감과 회의적인 시각도 존재함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외국인 매도', '국가 위기']</t>
+          <t>['FDA 승인', 'IR 발표', '외인']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41550</v>
+        <v>14950</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.96%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>211</v>
+        <v>153</v>
       </c>
       <c r="F15" t="n">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="G15" t="n">
-        <v>829</v>
+        <v>204</v>
       </c>
       <c r="H15" t="n">
-        <v>12.97</v>
+        <v>0.11</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>40750</v>
+        <v>14940</v>
       </c>
       <c r="K15" t="n">
-        <v>40600</v>
+        <v>14940</v>
       </c>
       <c r="L15" t="n">
-        <v>41650</v>
+        <v>16290</v>
       </c>
       <c r="M15" t="n">
-        <v>40050</v>
+        <v>14330</v>
       </c>
       <c r="N15" t="n">
-        <v>12.84</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>9106815150</v>
+        <v>39061214760</v>
       </c>
       <c r="P15" t="n">
-        <v>69200</v>
+        <v>30800</v>
       </c>
       <c r="Q15" t="n">
-        <v>24150</v>
+        <v>9810</v>
       </c>
       <c r="R15" t="n">
-        <v>15000</v>
+        <v>7000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>담관암 FDA 승인 기대감과 함께 외인 매수세 유입이 확인되었으나, 진양곤 회장 등 변수에 대한 불안감도 존재함.</t>
+          <t>높은 공모가, 상장 사기, 경영진 비판 등 부정적인 의견이 지배적이며, 실질적인 팩트 기반의 긍정적 언급은 없음.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['FDA 승인', '외인 매수', '담관암']</t>
+          <t>['공모가', '상장 사기', '경영진']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15030</v>
+        <v>20050</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.60%</t>
+          <t>'-3.37%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="E16" t="n">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="F16" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G16" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H16" t="n">
-        <v>0.11</v>
+        <v>4.28</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,139 +1883,139 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14940</v>
+        <v>20750</v>
       </c>
       <c r="K16" t="n">
-        <v>14940</v>
+        <v>20500</v>
       </c>
       <c r="L16" t="n">
-        <v>16290</v>
+        <v>21500</v>
       </c>
       <c r="M16" t="n">
-        <v>14330</v>
+        <v>19440</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O16" t="n">
-        <v>38901977810</v>
+        <v>35492881470</v>
       </c>
       <c r="P16" t="n">
-        <v>30800</v>
+        <v>22450</v>
       </c>
       <c r="Q16" t="n">
-        <v>9810</v>
+        <v>6320</v>
       </c>
       <c r="R16" t="n">
-        <v>7000</v>
+        <v>28000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>상장 사기 의혹 및 높은 공모가에 대한 비판과 함께 경영진 사퇴 요구.</t>
+          <t>농협, KDB 등 금융권 신규 납품 요청 및 보안 강화 트렌드 속 수혜 기대. 해킹 사고 증가 추세 및 프로그램 매매 관련 이슈.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['상장 사기', '공모가']</t>
+          <t>['보안', '신규 납품', '해킹 사고']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19910</v>
+        <v>65500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.05%</t>
+          <t>'-4.93%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2.5</v>
+        <v>-0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="F17" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="G17" t="n">
-        <v>194</v>
+        <v>360</v>
       </c>
       <c r="H17" t="n">
-        <v>4.28</v>
+        <v>22.1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>20750</v>
+        <v>68900</v>
       </c>
       <c r="K17" t="n">
-        <v>20500</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>19440</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.78</v>
+        <v>22.11</v>
       </c>
       <c r="O17" t="n">
-        <v>35149780600</v>
+        <v>81686000000</v>
       </c>
       <c r="P17" t="n">
-        <v>22450</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>6320</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>28000</v>
+        <v>50000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-24000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>농협, KDB 등 금융권 신규 납품 요청 및 보안 강화 트렌드 속 수혜 기대. 해킹 사고 증가 추세 및 프로그램 매매 관련 이슈.</t>
+          <t>원전 관련주로서의 기대와 함께 매출 하회, 외국계 증권사 매도 등의 부정적인 요인이 언급됨.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['보안', '신규 납품', '해킹 사고']</t>
+          <t>['원전', '매출', '외국계 증권사']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2056,10 +2056,10 @@
         <v>67</v>
       </c>
       <c r="G18" t="n">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="H18" t="n">
-        <v>53.46</v>
+        <v>53.45</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>96384128575</v>
+        <v>99897041600</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>
